--- a/data/studyInformation/studyInformation_publication.xlsx
+++ b/data/studyInformation/studyInformation_publication.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/441cc9bc8c67f6c4/Arbeit/Projekte/NIDER/NIDER_project/data/studyInformation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="113" documentId="13_ncr:1_{78E4A3AC-D6B7-44D5-B848-F46824049C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1ADD818A-DBCD-4626-AA94-3531A3DDE357}"/>
+  <xr:revisionPtr revIDLastSave="124" documentId="13_ncr:1_{78E4A3AC-D6B7-44D5-B848-F46824049C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71D816A0-31D9-4A96-A231-3E1DA755DD1B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StudyData" sheetId="1" r:id="rId1"/>
@@ -3440,34 +3440,34 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AB1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="45.109375" customWidth="1"/>
+    <col min="1" max="1" width="45.140625" customWidth="1"/>
     <col min="2" max="2" width="27" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" customWidth="1"/>
-    <col min="5" max="5" width="25.109375" customWidth="1"/>
-    <col min="6" max="7" width="15.88671875" customWidth="1"/>
-    <col min="8" max="8" width="19.44140625" customWidth="1"/>
-    <col min="9" max="9" width="16.88671875" customWidth="1"/>
-    <col min="10" max="10" width="24.44140625" customWidth="1"/>
-    <col min="11" max="11" width="22.6640625" customWidth="1"/>
-    <col min="12" max="12" width="38.6640625" customWidth="1"/>
-    <col min="13" max="13" width="54.44140625" customWidth="1"/>
-    <col min="14" max="14" width="44.6640625" customWidth="1"/>
-    <col min="15" max="15" width="49.44140625" customWidth="1"/>
-    <col min="16" max="16" width="63.5546875" customWidth="1"/>
-    <col min="17" max="17" width="42.6640625" customWidth="1"/>
-    <col min="18" max="18" width="27.6640625" customWidth="1"/>
-    <col min="19" max="19" width="23.5546875" customWidth="1"/>
-    <col min="20" max="20" width="38.109375" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" customWidth="1"/>
+    <col min="5" max="5" width="25.140625" customWidth="1"/>
+    <col min="6" max="7" width="15.85546875" customWidth="1"/>
+    <col min="8" max="8" width="19.42578125" customWidth="1"/>
+    <col min="9" max="9" width="16.85546875" customWidth="1"/>
+    <col min="10" max="10" width="24.42578125" customWidth="1"/>
+    <col min="11" max="11" width="22.7109375" customWidth="1"/>
+    <col min="12" max="12" width="38.7109375" customWidth="1"/>
+    <col min="13" max="13" width="54.42578125" customWidth="1"/>
+    <col min="14" max="14" width="44.7109375" customWidth="1"/>
+    <col min="15" max="15" width="49.42578125" customWidth="1"/>
+    <col min="16" max="16" width="63.5703125" customWidth="1"/>
+    <col min="17" max="17" width="42.7109375" customWidth="1"/>
+    <col min="18" max="18" width="27.7109375" customWidth="1"/>
+    <col min="19" max="19" width="23.5703125" customWidth="1"/>
+    <col min="20" max="20" width="38.140625" customWidth="1"/>
     <col min="21" max="21" width="41" customWidth="1"/>
-    <col min="22" max="24" width="11.109375" customWidth="1"/>
-    <col min="25" max="25" width="12.44140625" customWidth="1"/>
-    <col min="26" max="26" width="11.109375" customWidth="1"/>
+    <col min="22" max="24" width="11.140625" customWidth="1"/>
+    <col min="25" max="25" width="12.42578125" customWidth="1"/>
+    <col min="26" max="26" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3547,7 +3547,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>26</v>
       </c>
@@ -3611,7 +3611,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>39</v>
       </c>
@@ -3688,7 +3688,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>55</v>
       </c>
@@ -3750,7 +3750,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>66</v>
       </c>
@@ -3827,7 +3827,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>84</v>
       </c>
@@ -3907,7 +3907,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>104</v>
       </c>
@@ -3981,7 +3981,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>104</v>
       </c>
@@ -4055,7 +4055,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>127</v>
       </c>
@@ -4114,7 +4114,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>137</v>
       </c>
@@ -4194,7 +4194,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>153</v>
       </c>
@@ -4247,7 +4247,6 @@
         <v>164</v>
       </c>
       <c r="W11" s="10"/>
-      <c r="X11" s="10"/>
       <c r="Y11" s="25" t="s">
         <v>37</v>
       </c>
@@ -4255,7 +4254,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>153</v>
       </c>
@@ -4316,7 +4315,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>172</v>
       </c>
@@ -4396,7 +4395,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="14" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>187</v>
       </c>
@@ -4455,7 +4454,7 @@
       </c>
       <c r="Z14" s="12"/>
     </row>
-    <row r="15" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>198</v>
       </c>
@@ -4520,7 +4519,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>211</v>
       </c>
@@ -4600,7 +4599,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>227</v>
       </c>
@@ -4673,7 +4672,7 @@
       <c r="Y17" s="12"/>
       <c r="Z17" s="12"/>
     </row>
-    <row r="18" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>239</v>
       </c>
@@ -4750,7 +4749,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>253</v>
       </c>
@@ -4827,7 +4826,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="20" spans="1:28" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:28" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>270</v>
       </c>
@@ -4907,7 +4906,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>285</v>
       </c>
@@ -4987,7 +4986,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="22" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>304</v>
       </c>
@@ -5067,7 +5066,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="23" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>304</v>
       </c>
@@ -5148,7 +5147,7 @@
       </c>
       <c r="AB23" s="75"/>
     </row>
-    <row r="24" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>304</v>
       </c>
@@ -5228,7 +5227,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="25" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>304</v>
       </c>
@@ -5308,7 +5307,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>304</v>
       </c>
@@ -5388,7 +5387,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="27" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>304</v>
       </c>
@@ -5468,7 +5467,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="28" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="14" t="s">
         <v>365</v>
       </c>
@@ -5545,7 +5544,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="1:28" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:28" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>378</v>
       </c>
@@ -5620,7 +5619,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="30" spans="1:28" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:28" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>389</v>
       </c>
@@ -5697,7 +5696,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="31" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>404</v>
       </c>
@@ -5777,7 +5776,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="32" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>423</v>
       </c>
@@ -5857,7 +5856,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="33" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>440</v>
       </c>
@@ -5929,7 +5928,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="34" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>440</v>
       </c>
@@ -6001,7 +6000,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>464</v>
       </c>
@@ -6081,7 +6080,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="36" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>478</v>
       </c>
@@ -6161,7 +6160,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="37" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>491</v>
       </c>
@@ -6241,7 +6240,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="38" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="77" t="s">
         <v>508</v>
       </c>
@@ -6316,7 +6315,7 @@
       </c>
       <c r="Z38" s="12"/>
     </row>
-    <row r="39" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
         <v>526</v>
       </c>
@@ -6396,7 +6395,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>543</v>
       </c>
@@ -6476,7 +6475,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="41" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
         <v>543</v>
       </c>
@@ -6556,8 +6555,8 @@
         <v>83</v>
       </c>
     </row>
-    <row r="42" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="R43" s="21"/>
       <c r="S43" s="21"/>
       <c r="T43" s="21"/>
@@ -6568,983 +6567,983 @@
       <c r="Y43" s="21"/>
       <c r="Z43" s="21"/>
     </row>
-    <row r="44" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H44" s="6"/>
       <c r="I44" s="6"/>
       <c r="J44" s="6"/>
     </row>
-    <row r="45" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E47" s="14"/>
     </row>
-    <row r="48" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E48" s="14"/>
     </row>
-    <row r="49" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E49" s="14"/>
     </row>
-    <row r="50" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E50" s="14"/>
     </row>
-    <row r="51" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E51" s="14"/>
     </row>
-    <row r="52" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E52" s="14"/>
     </row>
-    <row r="53" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E53" s="14"/>
     </row>
-    <row r="54" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E54" s="14"/>
     </row>
-    <row r="55" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -7594,12 +7593,12 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A2:J8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="5" max="5" width="38.33203125" customWidth="1"/>
+    <col min="5" max="5" width="38.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -7631,7 +7630,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="6" t="s">
         <v>580</v>
       </c>
@@ -7645,7 +7644,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="21"/>
     </row>
   </sheetData>
@@ -7660,27 +7659,27 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:P1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.109375" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" customWidth="1"/>
     <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="11.109375" customWidth="1"/>
-    <col min="4" max="4" width="32.44140625" customWidth="1"/>
-    <col min="5" max="5" width="27.6640625" customWidth="1"/>
-    <col min="6" max="6" width="15.109375" customWidth="1"/>
-    <col min="7" max="7" width="12.5546875" customWidth="1"/>
-    <col min="8" max="8" width="11.109375" customWidth="1"/>
-    <col min="9" max="9" width="14.44140625" customWidth="1"/>
-    <col min="10" max="10" width="16.44140625" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" customWidth="1"/>
-    <col min="12" max="12" width="22.6640625" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" customWidth="1"/>
+    <col min="4" max="4" width="32.42578125" customWidth="1"/>
+    <col min="5" max="5" width="27.7109375" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" customWidth="1"/>
+    <col min="7" max="7" width="12.5703125" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" customWidth="1"/>
+    <col min="10" max="10" width="16.42578125" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" customWidth="1"/>
+    <col min="12" max="12" width="22.7109375" customWidth="1"/>
     <col min="13" max="13" width="15" customWidth="1"/>
-    <col min="14" max="14" width="11.109375" customWidth="1"/>
-    <col min="15" max="15" width="23.33203125" customWidth="1"/>
-    <col min="16" max="26" width="11.109375" customWidth="1"/>
+    <col min="14" max="14" width="11.140625" customWidth="1"/>
+    <col min="15" max="15" width="23.28515625" customWidth="1"/>
+    <col min="16" max="26" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="55" t="s">
         <v>584</v>
       </c>
@@ -7730,7 +7729,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="21" t="s">
         <v>28</v>
       </c>
@@ -7780,7 +7779,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="21" t="s">
         <v>41</v>
       </c>
@@ -7830,7 +7829,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="21" t="s">
         <v>57</v>
       </c>
@@ -7851,7 +7850,7 @@
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
     </row>
-    <row r="5" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="21" t="s">
         <v>68</v>
       </c>
@@ -7860,14 +7859,14 @@
       </c>
       <c r="C5" s="21"/>
     </row>
-    <row r="6" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="21" t="s">
         <v>613</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
     </row>
-    <row r="7" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>106</v>
       </c>
@@ -7917,7 +7916,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>106</v>
       </c>
@@ -7967,7 +7966,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>129</v>
       </c>
@@ -8017,7 +8016,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="21" t="s">
         <v>630</v>
       </c>
@@ -8030,7 +8029,7 @@
       <c r="L10" s="21"/>
       <c r="M10" s="21"/>
     </row>
-    <row r="11" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="21" t="s">
         <v>631</v>
       </c>
@@ -8080,7 +8079,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="21" t="s">
         <v>631</v>
       </c>
@@ -8130,7 +8129,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="21" t="s">
         <v>174</v>
       </c>
@@ -8180,7 +8179,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="21" t="s">
         <v>188</v>
       </c>
@@ -8226,7 +8225,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="21" t="s">
         <v>656</v>
       </c>
@@ -8276,7 +8275,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="21" t="s">
         <v>213</v>
       </c>
@@ -8326,12 +8325,12 @@
         <v>612</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="21" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="21" t="s">
         <v>666</v>
       </c>
@@ -8340,7 +8339,7 @@
       </c>
       <c r="C18" s="4"/>
     </row>
-    <row r="19" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="21" t="s">
         <v>255</v>
       </c>
@@ -8349,7 +8348,7 @@
       </c>
       <c r="C19" s="4"/>
     </row>
-    <row r="20" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>272</v>
       </c>
@@ -8399,7 +8398,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="21" t="s">
         <v>287</v>
       </c>
@@ -8408,7 +8407,7 @@
       </c>
       <c r="C21" s="4"/>
     </row>
-    <row r="22" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>305</v>
       </c>
@@ -8458,7 +8457,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>305</v>
       </c>
@@ -8508,7 +8507,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>305</v>
       </c>
@@ -8558,7 +8557,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>305</v>
       </c>
@@ -8608,7 +8607,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>305</v>
       </c>
@@ -8658,7 +8657,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>305</v>
       </c>
@@ -8708,7 +8707,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>705</v>
       </c>
@@ -8758,7 +8757,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>380</v>
       </c>
@@ -8790,7 +8789,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>711</v>
       </c>
@@ -8798,7 +8797,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>406</v>
       </c>
@@ -8806,7 +8805,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>425</v>
       </c>
@@ -8856,7 +8855,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="65" t="s">
         <v>720</v>
       </c>
@@ -8903,7 +8902,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="65" t="s">
         <v>720</v>
       </c>
@@ -8950,7 +8949,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>466</v>
       </c>
@@ -9000,7 +8999,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>730</v>
       </c>
@@ -9008,7 +9007,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>493</v>
       </c>
@@ -9052,7 +9051,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>509</v>
       </c>
@@ -9102,7 +9101,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
         <v>522</v>
       </c>
@@ -9152,7 +9151,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>748</v>
       </c>
@@ -9202,7 +9201,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
         <v>757</v>
       </c>
@@ -9210,7 +9209,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>757</v>
       </c>
@@ -9218,12 +9217,12 @@
         <v>381</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="67" t="s">
         <v>758</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="68" t="s">
         <v>613</v>
       </c>
@@ -9231,7 +9230,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="68" t="s">
         <v>630</v>
       </c>
@@ -9240,7 +9239,7 @@
       </c>
       <c r="C45" s="21"/>
     </row>
-    <row r="46" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="68" t="s">
         <v>228</v>
       </c>
@@ -9249,7 +9248,7 @@
       </c>
       <c r="C46" s="21"/>
     </row>
-    <row r="47" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="68" t="s">
         <v>760</v>
       </c>
@@ -9258,7 +9257,7 @@
       </c>
       <c r="C47" s="21"/>
     </row>
-    <row r="48" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="68" t="s">
         <v>705</v>
       </c>
@@ -9267,970 +9266,970 @@
       </c>
       <c r="C48" s="21"/>
     </row>
-    <row r="49" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="68"/>
       <c r="B49" s="21"/>
       <c r="C49" s="21"/>
     </row>
-    <row r="50" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="68"/>
       <c r="B50" s="21"/>
       <c r="C50" s="21"/>
     </row>
-    <row r="51" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="65"/>
       <c r="B51" s="21"/>
       <c r="C51" s="21"/>
     </row>
-    <row r="52" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
@@ -10269,20 +10268,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B0260D3-B8DC-4930-82AA-9DE305117714}">
   <dimension ref="A1:W98"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="12.88671875" customWidth="1"/>
-    <col min="5" max="5" width="19.33203125" customWidth="1"/>
-    <col min="6" max="6" width="24.6640625" customWidth="1"/>
-    <col min="7" max="7" width="23.44140625" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" customWidth="1"/>
-    <col min="10" max="10" width="32.88671875" customWidth="1"/>
-    <col min="11" max="12" width="21.33203125" customWidth="1"/>
-    <col min="13" max="13" width="18.6640625" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" customWidth="1"/>
+    <col min="6" max="6" width="24.7109375" customWidth="1"/>
+    <col min="7" max="7" width="23.42578125" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" customWidth="1"/>
+    <col min="10" max="10" width="32.85546875" customWidth="1"/>
+    <col min="11" max="12" width="21.28515625" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
     <col min="14" max="14" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1" t="s">
@@ -10327,7 +10326,7 @@
       </c>
       <c r="W1" s="1"/>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4" t="s">
@@ -10372,7 +10371,7 @@
       </c>
       <c r="W2" s="10"/>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4" t="s">
@@ -10417,7 +10416,7 @@
       </c>
       <c r="W3" s="10"/>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4" t="s">
@@ -10461,7 +10460,7 @@
       </c>
       <c r="W4" s="10"/>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4" t="s">
@@ -10503,7 +10502,7 @@
       <c r="T5" s="4"/>
       <c r="W5" s="10"/>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="77" t="s">
@@ -10548,7 +10547,7 @@
       </c>
       <c r="W6" s="10"/>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4" t="s">
@@ -10593,7 +10592,7 @@
       </c>
       <c r="W7" s="10"/>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4" t="s">
@@ -10638,7 +10637,7 @@
       </c>
       <c r="W8" s="10"/>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
       <c r="B9" s="22"/>
       <c r="C9" s="4" t="s">
@@ -10682,7 +10681,7 @@
       </c>
       <c r="W9" s="10"/>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4" t="s">
@@ -10727,7 +10726,7 @@
       </c>
       <c r="W10" s="10"/>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4" t="s">
@@ -10768,7 +10767,7 @@
       </c>
       <c r="W11" s="10"/>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4" t="s">
@@ -10809,7 +10808,7 @@
       </c>
       <c r="W12" s="10"/>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4" t="s">
@@ -10854,7 +10853,7 @@
       </c>
       <c r="W13" s="10"/>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4" t="s">
@@ -10891,7 +10890,7 @@
       </c>
       <c r="W14" s="10"/>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4" t="s">
@@ -10935,7 +10934,7 @@
       </c>
       <c r="W15" s="10"/>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4" t="s">
@@ -10980,7 +10979,7 @@
       </c>
       <c r="W16" s="10"/>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4" t="s">
@@ -11019,7 +11018,7 @@
       <c r="T17" s="4"/>
       <c r="W17" s="10"/>
     </row>
-    <row r="18" spans="1:23" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:23" ht="15" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4" t="s">
@@ -11061,7 +11060,7 @@
       <c r="T18" s="28"/>
       <c r="W18" s="10"/>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4" t="s">
@@ -11103,7 +11102,7 @@
       <c r="T19" s="4"/>
       <c r="W19" s="10"/>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4" t="s">
@@ -11148,7 +11147,7 @@
       </c>
       <c r="W20" s="9"/>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A21" s="4"/>
       <c r="B21" s="21"/>
       <c r="C21" s="21" t="s">
@@ -11193,7 +11192,7 @@
       </c>
       <c r="W21" s="10"/>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4" t="s">
@@ -11238,7 +11237,7 @@
       </c>
       <c r="W22" s="10"/>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4" t="s">
@@ -11283,7 +11282,7 @@
       </c>
       <c r="W23" s="10"/>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4" t="s">
@@ -11328,7 +11327,7 @@
       </c>
       <c r="W24" s="10"/>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4" t="s">
@@ -11373,7 +11372,7 @@
       </c>
       <c r="W25" s="10"/>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4" t="s">
@@ -11418,7 +11417,7 @@
       </c>
       <c r="W26" s="10"/>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4" t="s">
@@ -11463,7 +11462,7 @@
       </c>
       <c r="W27" s="10"/>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A28" s="14"/>
       <c r="B28" s="14"/>
       <c r="C28" s="14" t="s">
@@ -11505,7 +11504,7 @@
       <c r="T28" s="14"/>
       <c r="W28" s="10"/>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4" t="s">
@@ -11547,7 +11546,7 @@
       <c r="T29" s="4"/>
       <c r="W29" s="10"/>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4" t="s">
@@ -11589,7 +11588,7 @@
       <c r="T30" s="4"/>
       <c r="W30" s="10"/>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4" t="s">
@@ -11634,7 +11633,7 @@
       </c>
       <c r="W31" s="10"/>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4" t="s">
@@ -11679,7 +11678,7 @@
       </c>
       <c r="W32" s="10"/>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A33" s="4"/>
       <c r="B33" s="42"/>
       <c r="C33" s="21" t="s">
@@ -11724,7 +11723,7 @@
       </c>
       <c r="W33" s="10"/>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A34" s="4"/>
       <c r="B34" s="23"/>
       <c r="C34" s="21" t="s">
@@ -11769,7 +11768,7 @@
       </c>
       <c r="W34" s="10"/>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
       <c r="B35" s="45"/>
       <c r="C35" s="4" t="s">
@@ -11814,7 +11813,7 @@
       </c>
       <c r="W35" s="10"/>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4" t="s">
@@ -11859,7 +11858,7 @@
       </c>
       <c r="W36" s="20"/>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4" t="s">
@@ -11904,7 +11903,7 @@
       </c>
       <c r="W37" s="10"/>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4" t="s">
@@ -11943,7 +11942,7 @@
       <c r="T38" s="4"/>
       <c r="W38" s="10"/>
     </row>
-    <row r="39" spans="1:23" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:23" ht="51" x14ac:dyDescent="0.2">
       <c r="A39" s="4"/>
       <c r="B39" s="47"/>
       <c r="C39" s="47" t="s">
@@ -11988,7 +11987,7 @@
       </c>
       <c r="W39" s="10"/>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4" t="s">
@@ -12033,7 +12032,7 @@
       </c>
       <c r="W40" s="10"/>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4" t="s">
@@ -12078,7 +12077,7 @@
       </c>
       <c r="W41" s="50"/>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>2</v>
       </c>
@@ -12116,7 +12115,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A53" t="str">
         <f>IF(COUNTA(B53)=1,"x", "")</f>
         <v/>
@@ -12158,7 +12157,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A54" t="str">
         <f t="shared" ref="A54:A92" si="0">IF(COUNTA(B54)=1,"x", "")</f>
         <v>x</v>
@@ -12203,7 +12202,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A55" t="str">
         <f t="shared" si="0"/>
         <v>x</v>
@@ -12248,7 +12247,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A56" t="str">
         <f t="shared" si="0"/>
         <v>x</v>
@@ -12293,7 +12292,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A57" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -12335,7 +12334,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A58" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -12377,7 +12376,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A59" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -12419,7 +12418,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A60" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -12461,7 +12460,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A61" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -12503,7 +12502,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A62" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -12542,7 +12541,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A63" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -12581,7 +12580,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A64" t="str">
         <f t="shared" si="0"/>
         <v>x</v>
@@ -12626,7 +12625,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A65" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -12661,7 +12660,7 @@
       <c r="L65" s="14"/>
       <c r="M65" s="14"/>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A66" t="str">
         <f t="shared" si="0"/>
         <v>x</v>
@@ -12706,7 +12705,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A67" t="str">
         <f t="shared" si="0"/>
         <v>x</v>
@@ -12751,7 +12750,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A68" t="str">
         <f t="shared" si="0"/>
         <v>x</v>
@@ -12793,7 +12792,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A69" t="str">
         <f t="shared" si="0"/>
         <v>x</v>
@@ -12838,7 +12837,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A70" t="str">
         <f t="shared" si="0"/>
         <v>x</v>
@@ -12883,7 +12882,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A71" t="str">
         <f t="shared" si="0"/>
         <v>x</v>
@@ -12928,7 +12927,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A72" t="str">
         <f t="shared" si="0"/>
         <v>x</v>
@@ -12973,7 +12972,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A73" t="str">
         <f t="shared" si="0"/>
         <v>x</v>
@@ -13018,7 +13017,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A74" t="str">
         <f t="shared" si="0"/>
         <v>x</v>
@@ -13063,7 +13062,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A75" t="str">
         <f t="shared" si="0"/>
         <v>x</v>
@@ -13108,7 +13107,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A76" t="str">
         <f t="shared" si="0"/>
         <v>x</v>
@@ -13153,7 +13152,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A77" t="str">
         <f t="shared" si="0"/>
         <v>x</v>
@@ -13198,7 +13197,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A78" t="str">
         <f t="shared" si="0"/>
         <v>x</v>
@@ -13243,7 +13242,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A79" t="str">
         <f t="shared" si="0"/>
         <v>x</v>
@@ -13288,7 +13287,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A80" t="str">
         <f t="shared" si="0"/>
         <v>x</v>
@@ -13333,7 +13332,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A81" t="str">
         <f t="shared" si="0"/>
         <v>x</v>
@@ -13378,7 +13377,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A82" t="str">
         <f t="shared" si="0"/>
         <v>x</v>
@@ -13423,7 +13422,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A83" t="str">
         <f t="shared" si="0"/>
         <v>x</v>
@@ -13468,7 +13467,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A84" t="str">
         <f t="shared" si="0"/>
         <v>x</v>
@@ -13513,7 +13512,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A85" t="str">
         <f t="shared" si="0"/>
         <v>x</v>
@@ -13558,7 +13557,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A86" t="str">
         <f t="shared" si="0"/>
         <v>x</v>
@@ -13603,7 +13602,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A87" t="str">
         <f t="shared" si="0"/>
         <v>x</v>
@@ -13648,7 +13647,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A88" t="str">
         <f t="shared" si="0"/>
         <v>x</v>
@@ -13693,7 +13692,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A89" t="str">
         <f t="shared" si="0"/>
         <v>x</v>
@@ -13735,7 +13734,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="90" spans="1:14" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A90" t="str">
         <f t="shared" si="0"/>
         <v>x</v>
@@ -13780,7 +13779,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A91" t="str">
         <f t="shared" si="0"/>
         <v>x</v>
@@ -13825,7 +13824,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A92" t="str">
         <f t="shared" si="0"/>
         <v>x</v>
@@ -13870,19 +13869,19 @@
         <v>83</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
       <c r="E95" s="88">
         <f>SUM(Tabelle1[sample size quest])</f>
         <v>2234</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
       <c r="E96" s="88">
         <f>E95-E74</f>
         <v>2175</v>
       </c>
     </row>
-    <row r="98" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E98">
         <f>COUNTA(Tabelle1[sample size quest])</f>
         <v>40</v>
@@ -13936,164 +13935,164 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:A32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>763</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="14" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="21" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="23" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="24" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="25" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="26" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="27" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>764</v>
       </c>
     </row>
-    <row r="28" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="29" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="30" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="31" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="32" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>543</v>
       </c>
@@ -14106,9 +14105,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB3829FE-2825-44B6-9E5F-7F134326CA19}">
   <dimension ref="A1:E41"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -14119,7 +14118,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>32</v>
       </c>
@@ -14130,7 +14129,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>45</v>
       </c>
@@ -14141,12 +14140,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="6"/>
       <c r="B4" s="4"/>
       <c r="C4" s="10"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>45</v>
       </c>
@@ -14157,7 +14156,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>32</v>
       </c>
@@ -14168,7 +14167,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>32</v>
       </c>
@@ -14179,7 +14178,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>32</v>
       </c>
@@ -14190,7 +14189,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>32</v>
       </c>
@@ -14201,7 +14200,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>32</v>
       </c>
@@ -14212,7 +14211,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>45</v>
       </c>
@@ -14223,7 +14222,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>45</v>
       </c>
@@ -14234,7 +14233,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>45</v>
       </c>
@@ -14245,7 +14244,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>195</v>
       </c>
@@ -14253,7 +14252,7 @@
       <c r="C14" s="14"/>
       <c r="E14" s="75"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>206</v>
       </c>
@@ -14264,7 +14263,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>45</v>
       </c>
@@ -14275,7 +14274,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>231</v>
       </c>
@@ -14286,7 +14285,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
         <v>32</v>
       </c>
@@ -14297,7 +14296,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>32</v>
       </c>
@@ -14308,12 +14307,12 @@
         <v>259</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="9"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="21" t="s">
         <v>765</v>
       </c>
@@ -14324,7 +14323,7 @@
         <v>5.98</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>45</v>
       </c>
@@ -14335,7 +14334,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>45</v>
       </c>
@@ -14346,7 +14345,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>45</v>
       </c>
@@ -14357,7 +14356,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>45</v>
       </c>
@@ -14368,7 +14367,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>45</v>
       </c>
@@ -14379,7 +14378,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>45</v>
       </c>
@@ -14390,7 +14389,7 @@
         <v>44866</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="14" t="s">
         <v>32</v>
       </c>
@@ -14401,7 +14400,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>45</v>
       </c>
@@ -14412,7 +14411,7 @@
         <v>0.94</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>45</v>
       </c>
@@ -14423,7 +14422,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>32</v>
       </c>
@@ -14434,7 +14433,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>32</v>
       </c>
@@ -14445,7 +14444,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="21" t="s">
         <v>447</v>
       </c>
@@ -14456,7 +14455,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="21" t="s">
         <v>447</v>
       </c>
@@ -14467,12 +14466,12 @@
         <v>460</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
       <c r="B35" s="15"/>
       <c r="C35" s="14"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>32</v>
       </c>
@@ -14483,17 +14482,17 @@
         <v>483</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="4"/>
       <c r="B38" s="15"/>
       <c r="C38" s="14"/>
     </row>
-    <row r="39" spans="1:3" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A39" s="47" t="s">
         <v>32</v>
       </c>
@@ -14504,12 +14503,12 @@
         <v>535</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" s="4"/>
       <c r="B40" s="20"/>
       <c r="C40" s="20"/>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" s="4"/>
       <c r="B41" s="14"/>
       <c r="C41" s="14"/>
